--- a/supplementary-material/Supplementary Table S9.xlsx
+++ b/supplementary-material/Supplementary Table S9.xlsx
@@ -3,12 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6531F26-F8D6-2C46-9AC0-278827B26841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huhuiling/AI_Employment/4 paper：VR WCE/Supplement827/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9D1775-46EB-5C41-8B0A-DF6035A50BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="7580" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16240" yWindow="4960" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="raw88_k3" sheetId="1" r:id="rId1"/>
+    <sheet name="PCA90_K2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -17,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
-    <t>Sup5_raw88_k3</t>
+    <t>PCA90 cluster assignments (K = 2)</t>
   </si>
   <si>
     <t>Video</t>
@@ -2409,7 +2414,7 @@
         <v>213.41069638259901</v>
       </c>
       <c r="CM3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN3" s="5">
         <v>-1.15175905156082</v>
@@ -2690,7 +2695,7 @@
         <v>258.96999073371097</v>
       </c>
       <c r="CM4" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN4" s="11">
         <v>-0.81886768990575598</v>
@@ -2971,7 +2976,7 @@
         <v>260.04423991656802</v>
       </c>
       <c r="CM5" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN5" s="11">
         <v>1.2521595939888399</v>
@@ -3252,7 +3257,7 @@
         <v>324.39653879142702</v>
       </c>
       <c r="CM6" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN6" s="11">
         <v>1.04942668762448</v>
@@ -3533,7 +3538,7 @@
         <v>223.07904834861699</v>
       </c>
       <c r="CM7" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN7" s="11">
         <v>-3.1779413366794702</v>
@@ -3814,7 +3819,7 @@
         <v>227.25761750155999</v>
       </c>
       <c r="CM8" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN8" s="11">
         <v>-4.3515530455607196</v>
@@ -4095,7 +4100,7 @@
         <v>258.34830589414503</v>
       </c>
       <c r="CM9" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN9" s="11">
         <v>-0.99814487583955702</v>
@@ -4376,7 +4381,7 @@
         <v>259.18678862401902</v>
       </c>
       <c r="CM10" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN10" s="11">
         <v>-1.23008833942106</v>
@@ -4657,7 +4662,7 @@
         <v>234.25770196004399</v>
       </c>
       <c r="CM11" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN11" s="11">
         <v>-2.4949139206284898</v>
@@ -5219,7 +5224,7 @@
         <v>228.598759874194</v>
       </c>
       <c r="CM13" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN13" s="11">
         <v>0.85446328788013004</v>
@@ -5500,7 +5505,7 @@
         <v>226.65915358536299</v>
       </c>
       <c r="CM14" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN14" s="11">
         <v>-0.99682847200713598</v>
@@ -5781,7 +5786,7 @@
         <v>261.290110078834</v>
       </c>
       <c r="CM15" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN15" s="11">
         <v>0.31021051781637299</v>
@@ -6062,7 +6067,7 @@
         <v>233.205867343314</v>
       </c>
       <c r="CM16" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN16" s="11">
         <v>-1.1825538774208999</v>
@@ -6343,7 +6348,7 @@
         <v>241.47161928907099</v>
       </c>
       <c r="CM17" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN17" s="11">
         <v>-0.245133061510002</v>
@@ -6624,7 +6629,7 @@
         <v>282.34677749616299</v>
       </c>
       <c r="CM18" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN18" s="11">
         <v>4.0547102043103802</v>
@@ -6905,7 +6910,7 @@
         <v>240.14141372289299</v>
       </c>
       <c r="CM19" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN19" s="11">
         <v>-1.5713076519320099</v>
@@ -7186,7 +7191,7 @@
         <v>242.11129408405799</v>
       </c>
       <c r="CM20" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN20" s="11">
         <v>-1.79353813836995</v>
@@ -8029,7 +8034,7 @@
         <v>240.15994142902201</v>
       </c>
       <c r="CM23" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN23" s="11">
         <v>-2.3542352658748502</v>
@@ -8591,7 +8596,7 @@
         <v>215.36167927653599</v>
       </c>
       <c r="CM25" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN25" s="11">
         <v>-2.85143979751179</v>
@@ -8872,7 +8877,7 @@
         <v>191.244646363946</v>
       </c>
       <c r="CM26" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN26" s="11">
         <v>-3.3131252177071402</v>
@@ -9153,7 +9158,7 @@
         <v>222.71798655167001</v>
       </c>
       <c r="CM27" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN27" s="11">
         <v>-1.6279802634659899</v>
@@ -9434,7 +9439,7 @@
         <v>267.84271395213398</v>
       </c>
       <c r="CM28" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN28" s="11">
         <v>0.87920249607630996</v>
@@ -9715,7 +9720,7 @@
         <v>254.69972325201701</v>
       </c>
       <c r="CM29" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN29" s="11">
         <v>0.98133705653496295</v>
@@ -9996,7 +10001,7 @@
         <v>250.46400960631999</v>
       </c>
       <c r="CM30" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN30" s="11">
         <v>-0.18561918157003701</v>
@@ -10277,7 +10282,7 @@
         <v>288.565153636974</v>
       </c>
       <c r="CM31" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN31" s="11">
         <v>1.4836802420580999</v>
@@ -10558,7 +10563,7 @@
         <v>215.75120247357501</v>
       </c>
       <c r="CM32" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN32" s="11">
         <v>-0.94936033286453003</v>
@@ -10839,7 +10844,7 @@
         <v>223.72215131188</v>
       </c>
       <c r="CM33" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN33" s="11">
         <v>0.59737673099509103</v>
@@ -11120,7 +11125,7 @@
         <v>264.43903713777797</v>
       </c>
       <c r="CM34" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN34" s="11">
         <v>2.99472578065483</v>
@@ -11963,7 +11968,7 @@
         <v>341.78863439531102</v>
       </c>
       <c r="CM37" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN37" s="11">
         <v>3.9406354529138601</v>
@@ -20112,7 +20117,7 @@
         <v>293.16481299216798</v>
       </c>
       <c r="CM66" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN66" s="11">
         <v>0.75468785256744497</v>
@@ -20393,7 +20398,7 @@
         <v>332.54884715319997</v>
       </c>
       <c r="CM67" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN67" s="11">
         <v>3.4421019163527999</v>
@@ -20674,7 +20679,7 @@
         <v>267.711893142397</v>
       </c>
       <c r="CM68" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN68" s="11">
         <v>-1.4068207178784</v>
@@ -20955,7 +20960,7 @@
         <v>258.90322416858402</v>
       </c>
       <c r="CM69" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN69" s="11">
         <v>-0.92753935140272203</v>
@@ -21236,7 +21241,7 @@
         <v>285.97578549357002</v>
       </c>
       <c r="CM70" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN70" s="11">
         <v>3.2289629430627702</v>
@@ -21517,7 +21522,7 @@
         <v>216.54972640879001</v>
       </c>
       <c r="CM71" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN71" s="11">
         <v>-2.27925041767514</v>
@@ -21798,7 +21803,7 @@
         <v>242.262185626182</v>
       </c>
       <c r="CM72" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN72" s="11">
         <v>-2.2991368185969701</v>
@@ -22360,7 +22365,7 @@
         <v>304.40361316142503</v>
       </c>
       <c r="CM74" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN74" s="11">
         <v>1.44761328659052</v>
@@ -24889,7 +24894,7 @@
         <v>303.783894027261</v>
       </c>
       <c r="CM83" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN83" s="11">
         <v>1.33743769545639</v>
@@ -25170,7 +25175,7 @@
         <v>323.39344134466302</v>
       </c>
       <c r="CM84" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN84" s="11">
         <v>2.4500666030899501</v>
@@ -25451,7 +25456,7 @@
         <v>322.25847975145899</v>
       </c>
       <c r="CM85" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN85" s="11">
         <v>2.0189536378662098</v>
@@ -26013,7 +26018,7 @@
         <v>344.21818547375301</v>
       </c>
       <c r="CM87" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN87" s="11">
         <v>2.8165372496594498</v>
@@ -26575,7 +26580,7 @@
         <v>276.74216632577998</v>
       </c>
       <c r="CM89" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN89" s="11">
         <v>2.5525616157983499</v>
@@ -27137,7 +27142,7 @@
         <v>330.01920685761598</v>
       </c>
       <c r="CM91" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN91" s="11">
         <v>3.5693510982848098</v>
@@ -27418,7 +27423,7 @@
         <v>267.93633666107303</v>
       </c>
       <c r="CM92" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN92" s="11">
         <v>2.8482294355325202</v>
@@ -27699,7 +27704,7 @@
         <v>251.8636744918</v>
       </c>
       <c r="CM93" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN93" s="11">
         <v>-2.0951524186703101</v>
@@ -27980,7 +27985,7 @@
         <v>313.43462893507302</v>
       </c>
       <c r="CM94" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN94" s="11">
         <v>0.56930674413720395</v>
@@ -28261,7 +28266,7 @@
         <v>259.29991233105301</v>
       </c>
       <c r="CM95" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN95" s="11">
         <v>0.31234218306293898</v>
@@ -28542,7 +28547,7 @@
         <v>251.89850086853801</v>
       </c>
       <c r="CM96" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN96" s="11">
         <v>-0.95702223657444296</v>
@@ -28823,7 +28828,7 @@
         <v>303.79813584662202</v>
       </c>
       <c r="CM97" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN97" s="11">
         <v>1.2841602651393</v>
@@ -29104,7 +29109,7 @@
         <v>232.54833262279999</v>
       </c>
       <c r="CM98" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN98" s="11">
         <v>-3.58134970997757</v>
@@ -29385,7 +29390,7 @@
         <v>240.72011948420899</v>
       </c>
       <c r="CM99" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN99" s="11">
         <v>-3.6721269538841201</v>
@@ -29947,7 +29952,7 @@
         <v>312.59434514833902</v>
       </c>
       <c r="CM101" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN101" s="11">
         <v>-0.52645557961558298</v>
@@ -30228,7 +30233,7 @@
         <v>212.62307707923901</v>
       </c>
       <c r="CM102" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN102" s="11">
         <v>-3.7952224703517201</v>
@@ -30509,7 +30514,7 @@
         <v>316.42780907954301</v>
       </c>
       <c r="CM103" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN103" s="11">
         <v>-0.20892875612829701</v>
@@ -30790,7 +30795,7 @@
         <v>282.23932458245201</v>
       </c>
       <c r="CM104" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN104" s="11">
         <v>0.62677124021403596</v>
@@ -31071,7 +31076,7 @@
         <v>260.26079619240898</v>
       </c>
       <c r="CM105" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN105" s="11">
         <v>1.1117932077813799</v>
@@ -31352,7 +31357,7 @@
         <v>281.49516019221801</v>
       </c>
       <c r="CM106" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN106" s="11">
         <v>0.860876653916823</v>
@@ -31633,7 +31638,7 @@
         <v>294.89597080505803</v>
       </c>
       <c r="CM107" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN107" s="11">
         <v>2.3358310919416101</v>
@@ -31914,7 +31919,7 @@
         <v>225.64176413079599</v>
       </c>
       <c r="CM108" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN108" s="11">
         <v>-2.88218385802507</v>
@@ -32195,7 +32200,7 @@
         <v>246.41598376442499</v>
       </c>
       <c r="CM109" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN109" s="11">
         <v>-1.1771009475033001</v>
@@ -32476,7 +32481,7 @@
         <v>244.90762466657699</v>
       </c>
       <c r="CM110" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN110" s="11">
         <v>-1.76020681173533</v>
@@ -32757,7 +32762,7 @@
         <v>258.66837626881301</v>
       </c>
       <c r="CM111" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN111" s="11">
         <v>-2.0640541598717799</v>
@@ -33319,7 +33324,7 @@
         <v>269.19513275367899</v>
       </c>
       <c r="CM113" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN113" s="11">
         <v>-1.5715153586588599</v>
@@ -33600,7 +33605,7 @@
         <v>266.17421121294001</v>
       </c>
       <c r="CM114" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN114" s="11">
         <v>3.4549077632094298</v>
@@ -33881,7 +33886,7 @@
         <v>242.26152096890399</v>
       </c>
       <c r="CM115" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN115" s="11">
         <v>0.76856504478008603</v>
@@ -34724,7 +34729,7 @@
         <v>287.67492504835201</v>
       </c>
       <c r="CM118" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN118" s="11">
         <v>1.80067826348536</v>
@@ -35005,7 +35010,7 @@
         <v>269.50445634897801</v>
       </c>
       <c r="CM119" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN119" s="11">
         <v>1.01903823986219</v>
@@ -35286,7 +35291,7 @@
         <v>263.82042711114798</v>
       </c>
       <c r="CM120" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN120" s="11">
         <v>-0.264218828291783</v>
@@ -35567,7 +35572,7 @@
         <v>256.36832661452098</v>
       </c>
       <c r="CM121" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN121" s="11">
         <v>0.48516591748832599</v>
@@ -35848,7 +35853,7 @@
         <v>287.93748679054198</v>
       </c>
       <c r="CM122" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN122" s="11">
         <v>3.4754522460541999</v>
@@ -36129,7 +36134,7 @@
         <v>263.44977187377401</v>
       </c>
       <c r="CM123" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN123" s="11">
         <v>1.82371703808956</v>
@@ -36410,7 +36415,7 @@
         <v>265.729152554834</v>
       </c>
       <c r="CM124" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN124" s="11">
         <v>2.8128621171050399</v>
@@ -36691,7 +36696,7 @@
         <v>271.74677750647402</v>
       </c>
       <c r="CM125" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN125" s="11">
         <v>2.645249054212</v>
@@ -37253,7 +37258,7 @@
         <v>329.46767755752398</v>
       </c>
       <c r="CM127" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN127" s="11">
         <v>-0.476605307999246</v>
@@ -37815,7 +37820,7 @@
         <v>281.19679773643099</v>
       </c>
       <c r="CM129" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN129" s="11">
         <v>-1.8648916660477299</v>
@@ -38096,7 +38101,7 @@
         <v>274.827574159562</v>
       </c>
       <c r="CM130" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN130" s="11">
         <v>-2.7664732081228798</v>
@@ -38658,7 +38663,7 @@
         <v>316.40983900103902</v>
       </c>
       <c r="CM132" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN132" s="11">
         <v>1.7880169265458501</v>
@@ -38939,7 +38944,7 @@
         <v>339.19126883442999</v>
       </c>
       <c r="CM133" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN133" s="11">
         <v>2.13657164418913</v>
@@ -39220,7 +39225,7 @@
         <v>326.908459815843</v>
       </c>
       <c r="CM134" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN134" s="11">
         <v>2.7032773935679302</v>
@@ -39501,7 +39506,7 @@
         <v>329.07509631047299</v>
       </c>
       <c r="CM135" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN135" s="11">
         <v>3.2228630106343501</v>
@@ -40344,7 +40349,7 @@
         <v>346.92565315210999</v>
       </c>
       <c r="CM138" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN138" s="11">
         <v>3.9260384813459899</v>
@@ -40625,7 +40630,7 @@
         <v>344.40866622785097</v>
       </c>
       <c r="CM139" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN139" s="11">
         <v>3.8808106864941401</v>
@@ -40906,7 +40911,7 @@
         <v>348.82663539441103</v>
       </c>
       <c r="CM140" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN140" s="11">
         <v>3.3782314458978302</v>
@@ -41187,7 +41192,7 @@
         <v>316.97842203258199</v>
       </c>
       <c r="CM141" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN141" s="11">
         <v>2.04361597654903</v>
@@ -41749,7 +41754,7 @@
         <v>296.73624371848302</v>
       </c>
       <c r="CM143" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN143" s="11">
         <v>2.6500171961455901</v>
@@ -42030,7 +42035,7 @@
         <v>356.81458265785801</v>
       </c>
       <c r="CM144" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN144" s="11">
         <v>1.51646110878961</v>
@@ -42592,7 +42597,7 @@
         <v>274.16294093125799</v>
       </c>
       <c r="CM146" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN146" s="11">
         <v>1.1920543753548301</v>
@@ -42873,7 +42878,7 @@
         <v>314.98740553754197</v>
       </c>
       <c r="CM147" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN147" s="11">
         <v>3.93581238295058</v>
@@ -43435,7 +43440,7 @@
         <v>293.156265471545</v>
       </c>
       <c r="CM149" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN149" s="11">
         <v>-0.49308298831987601</v>
@@ -45121,7 +45126,7 @@
         <v>331.86023744212901</v>
       </c>
       <c r="CM155" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN155" s="11">
         <v>3.4130758019106602</v>
@@ -45402,7 +45407,7 @@
         <v>351.90880999290198</v>
       </c>
       <c r="CM156" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN156" s="11">
         <v>3.1164724389234402</v>
@@ -45683,7 +45688,7 @@
         <v>338.14954279242698</v>
       </c>
       <c r="CM157" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN157" s="11">
         <v>2.4804053990378998</v>
@@ -45964,7 +45969,7 @@
         <v>336.39742782675302</v>
       </c>
       <c r="CM158" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN158" s="11">
         <v>2.7943899117548199</v>
@@ -47088,7 +47093,7 @@
         <v>346.315888515621</v>
       </c>
       <c r="CM162" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN162" s="11">
         <v>1.8446282171733199</v>
@@ -47931,7 +47936,7 @@
         <v>352.54921595998599</v>
       </c>
       <c r="CM165" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN165" s="11">
         <v>1.9021929924716601</v>
@@ -48212,7 +48217,7 @@
         <v>343.628304223312</v>
       </c>
       <c r="CM166" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN166" s="11">
         <v>3.6724902713102798</v>
@@ -48493,7 +48498,7 @@
         <v>365.63690682400397</v>
       </c>
       <c r="CM167" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN167" s="11">
         <v>3.4862181009014401</v>
@@ -53832,7 +53837,7 @@
         <v>281.85964030864398</v>
       </c>
       <c r="CM186" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN186" s="11">
         <v>-0.38013872237125101</v>
@@ -58890,7 +58895,7 @@
         <v>274.21850514528398</v>
       </c>
       <c r="CM204" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN204" s="11">
         <v>-3.9203443645166902</v>
@@ -60857,7 +60862,7 @@
         <v>224.060488835336</v>
       </c>
       <c r="CM211" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN211" s="11">
         <v>-3.2165418550804299</v>
@@ -63386,7 +63391,7 @@
         <v>252.842982403664</v>
       </c>
       <c r="CM220" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN220" s="11">
         <v>-2.2149874287515501</v>
@@ -63667,7 +63672,7 @@
         <v>287.419477886143</v>
       </c>
       <c r="CM221" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN221" s="11">
         <v>-2.3189010678647102</v>
@@ -64791,7 +64796,7 @@
         <v>232.31597999239099</v>
       </c>
       <c r="CM225" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN225" s="11">
         <v>-3.44230914995283</v>
@@ -65072,7 +65077,7 @@
         <v>218.301988527915</v>
       </c>
       <c r="CM226" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN226" s="11">
         <v>-2.65542983055935</v>
@@ -66477,7 +66482,7 @@
         <v>280.893373341737</v>
       </c>
       <c r="CM231" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN231" s="11">
         <v>-3.8117968789977899</v>
@@ -68725,7 +68730,7 @@
         <v>237.97977786596999</v>
       </c>
       <c r="CM239" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN239" s="11">
         <v>-3.35177217985389</v>
@@ -69287,7 +69292,7 @@
         <v>237.77680771756999</v>
       </c>
       <c r="CM241" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN241" s="11">
         <v>1.65524322700445E-2</v>
